--- a/References/Hybrid SDLC Agile Templates/TGI - CBTL - DAVID - Hybrid SDLC Agile.xlsx
+++ b/References/Hybrid SDLC Agile Templates/TGI - CBTL - DAVID - Hybrid SDLC Agile.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="157">
   <si>
     <t>Template Name</t>
   </si>
@@ -342,6 +342,12 @@
   </si>
   <si>
     <t>Use the matrix as the cross-department reporting view. Milestone marks the primary owning department and Waiting is the recommended initial state; replace these with current status or target week as planning progresses. Imported Sub-Tasks remain the source of progress percentages.</t>
+  </si>
+  <si>
+    <t>Parallel planning</t>
+  </si>
+  <si>
+    <t>Independent departmental readiness checkpoints run in parallel after the target workflow is approved. LINK HUB business processes also run as parallel workstreams; design/build/QA/UAT/release gates inside each process remain sequential.</t>
   </si>
   <si>
     <t>Task Board</t>
@@ -4161,15 +4167,15 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>113</v>
@@ -4192,8 +4198,12 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2"/>
@@ -4962,7 +4972,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4970,30 +4980,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5001,13 +5011,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5015,41 +5025,41 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6230,22 +6240,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6256,10 +6266,10 @@
         <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
         <v>34</v>
@@ -6270,30 +6280,30 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
         <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E3" t="s">
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
@@ -6301,7 +6311,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
